--- a/reports/telecom_report.xlsx
+++ b/reports/telecom_report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USERCO~1\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epanalyticservice-my.sharepoint.com/personal/epedraza_epnexo_dev/Documents/Claude flow/HTML Report/primer test/reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{91DFD360-9367-4FF1-88EC-8ACF53ABEA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{91DFD360-9367-4FF1-88EC-8ACF53ABEA89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{580F8A32-B8CA-4B8B-A355-873A42CE8AAF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{3E1A10EB-C8AA-48ED-9C97-EEB25AE1CF7E}"/>
   </bookViews>
@@ -28,20 +28,20 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="672" r:id="rId6"/>
-    <pivotCache cacheId="675" r:id="rId7"/>
-    <pivotCache cacheId="678" r:id="rId8"/>
-    <pivotCache cacheId="681" r:id="rId9"/>
-    <pivotCache cacheId="684" r:id="rId10"/>
-    <pivotCache cacheId="687" r:id="rId11"/>
-    <pivotCache cacheId="690" r:id="rId12"/>
-    <pivotCache cacheId="693" r:id="rId13"/>
-    <pivotCache cacheId="694" r:id="rId14"/>
+    <pivotCache cacheId="8" r:id="rId6"/>
+    <pivotCache cacheId="84" r:id="rId7"/>
+    <pivotCache cacheId="87" r:id="rId8"/>
+    <pivotCache cacheId="90" r:id="rId9"/>
+    <pivotCache cacheId="93" r:id="rId10"/>
+    <pivotCache cacheId="96" r:id="rId11"/>
+    <pivotCache cacheId="99" r:id="rId12"/>
+    <pivotCache cacheId="102" r:id="rId13"/>
+    <pivotCache cacheId="105" r:id="rId14"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="153" r:id="rId15"/>
+        <pivotCache cacheId="9" r:id="rId15"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -955,51 +955,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1024,6 +979,51 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,7 +1105,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[telecom_report_14592.xlsx]Pivots!ptMonth</c:name>
+    <c:name>[telecom_report.xlsx]Pivots!ptMonth</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1568,7 +1568,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[telecom_report_14592.xlsx]Pivots!ptRegion</c:name>
+    <c:name>[telecom_report.xlsx]Pivots!ptRegion</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1984,7 +1984,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[telecom_report_14592.xlsx]Pivots!ptFailure</c:name>
+    <c:name>[telecom_report.xlsx]Pivots!ptFailure</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2400,7 +2400,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[telecom_report_14592.xlsx]Pivots!ptProduct</c:name>
+    <c:name>[telecom_report.xlsx]Pivots!ptProduct</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2792,7 +2792,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[telecom_report_14592.xlsx]Pivots!ptStatus</c:name>
+    <c:name>[telecom_report.xlsx]Pivots!ptStatus</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -6429,8 +6429,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>148167</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="Region">
@@ -6453,7 +6453,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6507,8 +6507,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="Segment">
@@ -6531,7 +6531,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6585,8 +6585,8 @@
       <xdr:row>30</xdr:row>
       <xdr:rowOff>50799</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="8" name="Product">
@@ -6609,7 +6609,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6663,8 +6663,8 @@
       <xdr:row>38</xdr:row>
       <xdr:rowOff>110067</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="9" name="Channel">
@@ -6687,7 +6687,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6741,8 +6741,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>169334</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="10" name="Quarter">
@@ -6765,7 +6765,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -6990,9 +6990,1179 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720263310184" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{51EDA788-8E9C-4EF6-AC55-A83BDE3BB231}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" saveData="0" refreshedBy="userconect" refreshedDate="46297.720266203702" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" tupleCache="1" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{332B9412-FE82-4BFA-8003-132F3BBBCFFA}">
   <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="8">
+  <cacheFields count="2">
+    <cacheField name="[Measures].[MeasuresLevel]" caption="MeasuresLevel" numFmtId="0" hierarchy="6">
+      <sharedItems count="6">
+        <s v="[Measures].[Revenue]" c="Revenue"/>
+        <s v="[Measures].[Transaction Count]" c="Transaction Count"/>
+        <s v="[Measures].[Success Rate]" c="Success Rate"/>
+        <s v="[Measures].[Active Customers]" c="Active Customers"/>
+        <s v="[Measures].[Average Ticket]" c="Average Ticket"/>
+        <s v="[Measures].[Revenue Lost]" c="Revenue Lost"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="10" level="1">
+      <sharedItems count="3">
+        <s v="[Transactions].[region].&amp;[Adelaide]" c="Adelaide"/>
+        <s v="[Transactions].[region].&amp;[Brisbane]" c="Brisbane"/>
+        <s v="[Transactions].[region].&amp;[Hobart]" c="Hobart"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="39">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" allCaption="All" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures]" caption="Measures" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Measures].[__No measures defined]" dimensionUniqueName="[Measures]" displayFolder="" measures="1" count="1" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <tupleCache>
+    <entries count="24">
+      <n v="42723" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="0"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="4233" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="1"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="0.80888258918025047" in="2">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="2"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="889" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="3"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="12.477511682242991" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="4"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="5919.5" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="5"/>
+          <tpl hier="10" item="0"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="256.5" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="5"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="11.033505154639176" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="4"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="97" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="3"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="0.88382687927107062" in="2">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="2"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="439" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="1"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="4281" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="0"/>
+          <tpl hier="10" item="5"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="413.5" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="5"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="13.209129511677283" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="4"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="106" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="3"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="0.92534381139489197" in="2">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="2"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="509" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="1"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="6221.5" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="0"/>
+          <tpl hier="10" item="6"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="64" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="5"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="13.323970037453183" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="4"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="65" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="3"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="0.93356643356643354" in="2">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="2"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="286" in="1">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="1"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+      <n v="3557.5" in="0">
+        <tpls c="6">
+          <tpl hier="2" item="4"/>
+          <tpl fld="0" item="0"/>
+          <tpl hier="10" item="7"/>
+          <tpl hier="11" item="1"/>
+          <tpl hier="12" item="2"/>
+          <tpl hier="14" item="3"/>
+        </tpls>
+      </n>
+    </entries>
+    <sets count="8">
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[region].[All]}">
+        <tpls c="1">
+          <tpl hier="10" item="4294967295"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[customer_segment].[All]}">
+        <tpls c="1">
+          <tpl hier="11" item="4294967295"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[product_type].[All]}">
+        <tpls c="1">
+          <tpl hier="12" item="4294967295"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[channel].[All]}">
+        <tpls c="1">
+          <tpl hier="14" item="4294967295"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Calendar].[Quarter].[All]}">
+        <tpls c="1">
+          <tpl hier="2" item="4294967295"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[region].&amp;[Adelaide]}">
+        <tpls c="1">
+          <tpl fld="1" item="0"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[region].&amp;[Brisbane]}">
+        <tpls c="1">
+          <tpl fld="1" item="1"/>
+        </tpls>
+      </set>
+      <set count="1" maxRank="1" setDefinition="{[Transactions].[region].&amp;[Hobart]}">
+        <tpls c="1">
+          <tpl fld="1" item="2"/>
+        </tpls>
+      </set>
+    </sets>
+    <queryCache count="6">
+      <query mdx="[Measures].[Revenue]">
+        <tpls c="1">
+          <tpl fld="0" item="0"/>
+        </tpls>
+      </query>
+      <query mdx="[Measures].[Transaction Count]">
+        <tpls c="1">
+          <tpl fld="0" item="1"/>
+        </tpls>
+      </query>
+      <query mdx="[Measures].[Success Rate]">
+        <tpls c="1">
+          <tpl fld="0" item="2"/>
+        </tpls>
+      </query>
+      <query mdx="[Measures].[Active Customers]">
+        <tpls c="1">
+          <tpl fld="0" item="3"/>
+        </tpls>
+      </query>
+      <query mdx="[Measures].[Average Ticket]">
+        <tpls c="1">
+          <tpl fld="0" item="4"/>
+        </tpls>
+      </query>
+      <query mdx="[Measures].[Revenue Lost]">
+        <tpls c="1">
+          <tpl fld="0" item="5"/>
+        </tpls>
+      </query>
+    </queryCache>
+    <serverFormats count="3">
+      <serverFormat format="#,0.00"/>
+      <serverFormat format="#,0"/>
+      <serverFormat format="0.0%;-0.0%;0.0%"/>
+    </serverFormats>
+  </tupleCache>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720118287034" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{46B0385E-959F-4F80-A2BA-15BAD90194B9}">
+  <cacheSource type="external" connectionId="3">
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
+        <x14:sourceConnection name="ThisWorkbookDataModel"/>
+      </ext>
+    </extLst>
+  </cacheSource>
+  <cacheFields count="0"/>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="1292679989" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721855671298" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{048A9C5C-8C7B-4E48-BD43-E9457034845E}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="2">
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems count="8">
+        <s v="Adelaide"/>
+        <s v="Brisbane"/>
+        <s v="Canberra"/>
+        <s v="Hobart"/>
+        <s v="Melbourne"/>
+        <s v="Perth"/>
+        <s v="Sydney"/>
+        <s v="Unknown"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721856249998" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C2CF3132-B88E-4D13-A959-927111FDFC76}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="3">
+    <cacheField name="[Calendar].[YearMonth].[YearMonth]" caption="YearMonth" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems count="12">
+        <s v="2024-01"/>
+        <s v="2024-02"/>
+        <s v="2024-03"/>
+        <s v="2024-04"/>
+        <s v="2024-05"/>
+        <s v="2024-06"/>
+        <s v="2024-07"/>
+        <s v="2024-08"/>
+        <s v="2024-09"/>
+        <s v="2024-10"/>
+        <s v="2024-11"/>
+        <s v="2024-12"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.72185671296" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00520305-7A8B-4D41-A720-845551B17A94}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="3">
+    <cacheField name="[Transactions].[product_type].[product_type]" caption="product_type" numFmtId="0" hierarchy="11" level="1">
+      <sharedItems count="4">
+        <s v="Data Bundle"/>
+        <s v="Recharge"/>
+        <s v="SMS Bundle"/>
+        <s v="Voice Bundle"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721857060184" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{42D153DF-682F-4B55-83F4-43990731BAD2}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="3">
+    <cacheField name="[Transactions].[channel].[channel]" caption="channel" numFmtId="0" hierarchy="13" level="1">
+      <sharedItems count="4">
+        <s v="Agent"/>
+        <s v="Mobile App"/>
+        <s v="USSD"/>
+        <s v="Web"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721857523145" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{49723E36-2761-49DB-9A96-6BEF66DEC8F6}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="2">
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems count="8">
+        <s v="Adelaide"/>
+        <s v="Brisbane"/>
+        <s v="Canberra"/>
+        <s v="Hobart"/>
+        <s v="Melbourne"/>
+        <s v="Perth"/>
+        <s v="Sydney"/>
+        <s v="Unknown"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Failure Rate]" caption="Failure Rate" numFmtId="0" hierarchy="25" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721857870369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{CE358752-67F9-47B4-947E-AE5A235651A3}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="4">
+    <cacheField name="[Transactions].[channel].[channel]" caption="channel" numFmtId="0" hierarchy="13" level="1">
+      <sharedItems count="4">
+        <s v="Agent"/>
+        <s v="Mobile App"/>
+        <s v="USSD"/>
+        <s v="Web"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Transactions].[status].[status]" caption="status" numFmtId="0" hierarchy="16" level="1">
+      <sharedItems count="3">
+        <s v="Failed"/>
+        <s v="Reversed"/>
+        <s v="Successful"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Transaction Count]" caption="Transaction Count" numFmtId="0" hierarchy="20" level="32767"/>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721858333331" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{423ACCB0-8E38-4D1B-AB40-AEE1270B6DC1}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="7">
+    <cacheField name="[Transactions].[product_type].[product_type]" caption="product_type" numFmtId="0" hierarchy="11" level="1">
+      <sharedItems count="4">
+        <s v="Data Bundle"/>
+        <s v="Recharge"/>
+        <s v="SMS Bundle"/>
+        <s v="Voice Bundle"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Transactions].[bundle_name].[bundle_name]" caption="bundle_name" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems count="13">
+        <s v="Data 10GB Monthly"/>
+        <s v="Data 1GB Daily"/>
+        <s v="Data 2GB Weekly"/>
+        <s v="Data 40GB Monthly"/>
+        <s v="Data 6GB Monthly"/>
+        <s v="Recharge $1"/>
+        <s v="Recharge $10"/>
+        <s v="Recharge $2"/>
+        <s v="Recharge $20"/>
+        <s v="Recharge $5"/>
+        <s v="SMS 200"/>
+        <s v="Voice 100min"/>
+        <s v="Voice 300min"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Successful Txns]" caption="Successful Txns" numFmtId="0" hierarchy="21" level="32767"/>
+    <cacheField name="[Measures].[Average Ticket]" caption="Average Ticket" numFmtId="0" hierarchy="27" level="32767"/>
+    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
+    <cacheField name="[Measures].[Revenue Lost]" caption="Revenue Lost" numFmtId="0" hierarchy="31" level="32767"/>
+    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="38">
+    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="3">
+    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
+  </dimensions>
+  <measureGroups count="2">
+    <measureGroup name="Calendar" caption="Calendar"/>
+    <measureGroup name="Transactions" caption="Transactions"/>
+  </measureGroups>
+  <maps count="3">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="1" dimension="0"/>
+    <map measureGroup="1" dimension="2"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.721858564815" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{51EDA788-8E9C-4EF6-AC55-A83BDE3BB231}">
+  <cacheSource type="external" connectionId="3"/>
+  <cacheFields count="7">
     <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
       <sharedItems count="8">
         <s v="Adelaide"/>
@@ -7011,19 +8181,11 @@
     <cacheField name="[Measures].[Reversal Rate]" caption="Reversal Rate" numFmtId="0" hierarchy="26" level="32767"/>
     <cacheField name="[Measures].[Revenue Lost]" caption="Revenue Lost" numFmtId="0" hierarchy="31" level="32767"/>
     <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
   </cacheFields>
   <cacheHierarchies count="38">
     <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="7"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
@@ -7112,989 +8274,10 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720118287034" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{46B0385E-959F-4F80-A2BA-15BAD90194B9}">
-  <cacheSource type="external" connectionId="3">
-    <extLst>
-      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
-        <x14:sourceConnection name="ThisWorkbookDataModel"/>
-      </ext>
-    </extLst>
-  </cacheSource>
-  <cacheFields count="0"/>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="1292679989" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720263657407" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{048A9C5C-8C7B-4E48-BD43-E9457034845E}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="3">
-    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
-      <sharedItems count="8">
-        <s v="Adelaide"/>
-        <s v="Brisbane"/>
-        <s v="Canberra"/>
-        <s v="Hobart"/>
-        <s v="Melbourne"/>
-        <s v="Perth"/>
-        <s v="Sydney"/>
-        <s v="Unknown"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720264120369" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C2CF3132-B88E-4D13-A959-927111FDFC76}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="3">
-    <cacheField name="[Calendar].[YearMonth].[YearMonth]" caption="YearMonth" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="12">
-        <s v="2024-01"/>
-        <s v="2024-02"/>
-        <s v="2024-03"/>
-        <s v="2024-04"/>
-        <s v="2024-05"/>
-        <s v="2024-06"/>
-        <s v="2024-07"/>
-        <s v="2024-08"/>
-        <s v="2024-09"/>
-        <s v="2024-10"/>
-        <s v="2024-11"/>
-        <s v="2024-12"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720264467593" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{00520305-7A8B-4D41-A720-845551B17A94}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="3">
-    <cacheField name="[Transactions].[product_type].[product_type]" caption="product_type" numFmtId="0" hierarchy="11" level="1">
-      <sharedItems count="4">
-        <s v="Data Bundle"/>
-        <s v="Recharge"/>
-        <s v="SMS Bundle"/>
-        <s v="Voice Bundle"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720264814816" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{42D153DF-682F-4B55-83F4-43990731BAD2}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="3">
-    <cacheField name="[Transactions].[channel].[channel]" caption="channel" numFmtId="0" hierarchy="13" level="1">
-      <sharedItems count="4">
-        <s v="Agent"/>
-        <s v="Mobile App"/>
-        <s v="USSD"/>
-        <s v="Web"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720265162039" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{49723E36-2761-49DB-9A96-6BEF66DEC8F6}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="3">
-    <cacheField name="[Transactions].[region].[region]" caption="region" numFmtId="0" hierarchy="9" level="1">
-      <sharedItems count="8">
-        <s v="Adelaide"/>
-        <s v="Brisbane"/>
-        <s v="Canberra"/>
-        <s v="Hobart"/>
-        <s v="Melbourne"/>
-        <s v="Perth"/>
-        <s v="Sydney"/>
-        <s v="Unknown"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Failure Rate]" caption="Failure Rate" numFmtId="0" hierarchy="25" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720265509262" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{CE358752-67F9-47B4-947E-AE5A235651A3}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="4">
-    <cacheField name="[Transactions].[channel].[channel]" caption="channel" numFmtId="0" hierarchy="13" level="1">
-      <sharedItems count="4">
-        <s v="Agent"/>
-        <s v="Mobile App"/>
-        <s v="USSD"/>
-        <s v="Web"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Transactions].[status].[status]" caption="status" numFmtId="0" hierarchy="16" level="1">
-      <sharedItems count="3">
-        <s v="Failed"/>
-        <s v="Reversed"/>
-        <s v="Successful"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Transaction Count]" caption="Transaction Count" numFmtId="0" hierarchy="20" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="userconect" refreshedDate="46297.720265972224" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{423ACCB0-8E38-4D1B-AB40-AEE1270B6DC1}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="7">
-    <cacheField name="[Transactions].[product_type].[product_type]" caption="product_type" numFmtId="0" hierarchy="11" level="1">
-      <sharedItems count="4">
-        <s v="Data Bundle"/>
-        <s v="Recharge"/>
-        <s v="SMS Bundle"/>
-        <s v="Voice Bundle"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Transactions].[bundle_name].[bundle_name]" caption="bundle_name" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems count="13">
-        <s v="Data 10GB Monthly"/>
-        <s v="Data 1GB Daily"/>
-        <s v="Data 2GB Weekly"/>
-        <s v="Data 40GB Monthly"/>
-        <s v="Data 6GB Monthly"/>
-        <s v="Recharge $1"/>
-        <s v="Recharge $10"/>
-        <s v="Recharge $2"/>
-        <s v="Recharge $20"/>
-        <s v="Recharge $5"/>
-        <s v="SMS 200"/>
-        <s v="Voice 100min"/>
-        <s v="Voice 300min"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Successful Txns]" caption="Successful Txns" numFmtId="0" hierarchy="21" level="32767"/>
-    <cacheField name="[Measures].[Average Ticket]" caption="Average Ticket" numFmtId="0" hierarchy="27" level="32767"/>
-    <cacheField name="[Measures].[Revenue]" caption="Revenue" numFmtId="0" hierarchy="19" level="32767"/>
-    <cacheField name="[Measures].[Revenue Lost]" caption="Revenue Lost" numFmtId="0" hierarchy="31" level="32767"/>
-    <cacheField name="[Calendar].[Quarter].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="2" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="38">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="3">
-    <dimension name="Calendar" uniqueName="[Calendar]" caption="Calendar"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Transactions" uniqueName="[Transactions]" caption="Transactions"/>
-  </dimensions>
-  <measureGroups count="2">
-    <measureGroup name="Calendar" caption="Calendar"/>
-    <measureGroup name="Transactions" caption="Transactions"/>
-  </measureGroups>
-  <maps count="3">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="1" dimension="0"/>
-    <map measureGroup="1" dimension="2"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" invalid="1" saveData="0" refreshedBy="userconect" refreshedDate="46297.720266203702" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" tupleCache="1" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{332B9412-FE82-4BFA-8003-132F3BBBCFFA}">
-  <cacheSource type="external" connectionId="3"/>
-  <cacheFields count="1">
-    <cacheField name="[Measures].[MeasuresLevel]" caption="MeasuresLevel" numFmtId="0" hierarchy="6">
-      <sharedItems count="6">
-        <s v="[Measures].[Revenue]" c="Revenue"/>
-        <s v="[Measures].[Transaction Count]" c="Transaction Count"/>
-        <s v="[Measures].[Success Rate]" c="Success Rate"/>
-        <s v="[Measures].[Active Customers]" c="Active Customers"/>
-        <s v="[Measures].[Average Ticket]" c="Average Ticket"/>
-        <s v="[Measures].[Revenue Lost]" c="Revenue Lost"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="39">
-    <cacheHierarchy uniqueName="[Calendar].[Date]" caption="Date" attribute="1" time="1" defaultMemberUniqueName="[Calendar].[Date].[All]" allUniqueName="[Calendar].[Date].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Calendar].[Year].[All]" allUniqueName="[Calendar].[Year].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Calendar].[Quarter].[All]" allUniqueName="[Calendar].[Quarter].[All]" allCaption="All" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[MonthNo]" caption="MonthNo" attribute="1" defaultMemberUniqueName="[Calendar].[MonthNo].[All]" allUniqueName="[Calendar].[MonthNo].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[YearMonth]" caption="YearMonth" attribute="1" defaultMemberUniqueName="[Calendar].[YearMonth].[All]" allUniqueName="[Calendar].[YearMonth].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Calendar].[Weekday]" caption="Weekday" attribute="1" defaultMemberUniqueName="[Calendar].[Weekday].[All]" allUniqueName="[Calendar].[Weekday].[All]" dimensionUniqueName="[Calendar]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures]" caption="Measures" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Measures].[__No measures defined]" dimensionUniqueName="[Measures]" displayFolder="" measures="1" count="1" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Transactions].[transaction_id]" caption="transaction_id" attribute="1" defaultMemberUniqueName="[Transactions].[transaction_id].[All]" allUniqueName="[Transactions].[transaction_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[txn_date]" caption="txn_date" attribute="1" time="1" defaultMemberUniqueName="[Transactions].[txn_date].[All]" allUniqueName="[Transactions].[txn_date].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_id]" caption="customer_id" attribute="1" defaultMemberUniqueName="[Transactions].[customer_id].[All]" allUniqueName="[Transactions].[customer_id].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[region]" caption="region" attribute="1" defaultMemberUniqueName="[Transactions].[region].[All]" allUniqueName="[Transactions].[region].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[customer_segment]" caption="customer_segment" attribute="1" defaultMemberUniqueName="[Transactions].[customer_segment].[All]" allUniqueName="[Transactions].[customer_segment].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[product_type]" caption="product_type" attribute="1" defaultMemberUniqueName="[Transactions].[product_type].[All]" allUniqueName="[Transactions].[product_type].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[bundle_name]" caption="bundle_name" attribute="1" defaultMemberUniqueName="[Transactions].[bundle_name].[All]" allUniqueName="[Transactions].[bundle_name].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[channel]" caption="channel" attribute="1" defaultMemberUniqueName="[Transactions].[channel].[All]" allUniqueName="[Transactions].[channel].[All]" allCaption="All" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[data_volume_mb]" caption="data_volume_mb" attribute="1" defaultMemberUniqueName="[Transactions].[data_volume_mb].[All]" allUniqueName="[Transactions].[data_volume_mb].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount]" caption="amount" attribute="1" defaultMemberUniqueName="[Transactions].[amount].[All]" allUniqueName="[Transactions].[amount].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[status]" caption="status" attribute="1" defaultMemberUniqueName="[Transactions].[status].[All]" allUniqueName="[Transactions].[status].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[amount_flag]" caption="amount_flag" attribute="1" defaultMemberUniqueName="[Transactions].[amount_flag].[All]" allUniqueName="[Transactions].[amount_flag].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Transactions].[list_price]" caption="list_price" attribute="1" defaultMemberUniqueName="[Transactions].[list_price].[All]" allUniqueName="[Transactions].[list_price].[All]" dimensionUniqueName="[Transactions]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue]" caption="Revenue" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Transaction Count]" caption="Transaction Count" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Successful Txns]" caption="Successful Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failed Txns]" caption="Failed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Txns]" caption="Reversed Txns" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Success Rate]" caption="Success Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Failure Rate]" caption="Failure Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversal Rate]" caption="Reversal Rate" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Ticket]" caption="Average Ticket" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Active Customers]" caption="Active Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Buying Customers]" caption="Buying Customers" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue per Customer]" caption="Revenue per Customer" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Lost]" caption="Revenue Lost" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Reversed Amount]" caption="Reversed Amount" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue Prev Month]" caption="Revenue Prev Month" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Revenue MoM %]" caption="Revenue MoM %" measure="1" displayFolder="" measureGroup="Transactions" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Transactions]" caption="__XL_Count Transactions" measure="1" displayFolder="" measureGroup="Transactions" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Calendar]" caption="__XL_Count Calendar" measure="1" displayFolder="" measureGroup="Calendar" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <tupleCache>
-    <entries count="6">
-      <n v="42723" in="0">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="0"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-      <n v="4233" in="1">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="1"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-      <n v="0.80888258918025047" in="2">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="2"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-      <n v="889" in="1">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="3"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-      <n v="12.477511682242991" in="0">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="4"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-      <n v="5919.5" in="0">
-        <tpls c="6">
-          <tpl hier="2" item="4"/>
-          <tpl fld="0" item="5"/>
-          <tpl hier="10" item="0"/>
-          <tpl hier="11" item="1"/>
-          <tpl hier="12" item="2"/>
-          <tpl hier="14" item="3"/>
-        </tpls>
-      </n>
-    </entries>
-    <sets count="5">
-      <set count="1" maxRank="1" setDefinition="{[Transactions].[region].[All]}">
-        <tpls c="1">
-          <tpl hier="10" item="4294967295"/>
-        </tpls>
-      </set>
-      <set count="1" maxRank="1" setDefinition="{[Transactions].[customer_segment].[All]}">
-        <tpls c="1">
-          <tpl hier="11" item="4294967295"/>
-        </tpls>
-      </set>
-      <set count="1" maxRank="1" setDefinition="{[Transactions].[product_type].[All]}">
-        <tpls c="1">
-          <tpl hier="12" item="4294967295"/>
-        </tpls>
-      </set>
-      <set count="1" maxRank="1" setDefinition="{[Transactions].[channel].[All]}">
-        <tpls c="1">
-          <tpl hier="14" item="4294967295"/>
-        </tpls>
-      </set>
-      <set count="1" maxRank="1" setDefinition="{[Calendar].[Quarter].[All]}">
-        <tpls c="1">
-          <tpl hier="2" item="4294967295"/>
-        </tpls>
-      </set>
-    </sets>
-    <queryCache count="6">
-      <query mdx="[Measures].[Revenue]">
-        <tpls c="1">
-          <tpl fld="0" item="0"/>
-        </tpls>
-      </query>
-      <query mdx="[Measures].[Transaction Count]">
-        <tpls c="1">
-          <tpl fld="0" item="1"/>
-        </tpls>
-      </query>
-      <query mdx="[Measures].[Success Rate]">
-        <tpls c="1">
-          <tpl fld="0" item="2"/>
-        </tpls>
-      </query>
-      <query mdx="[Measures].[Active Customers]">
-        <tpls c="1">
-          <tpl fld="0" item="3"/>
-        </tpls>
-      </query>
-      <query mdx="[Measures].[Average Ticket]">
-        <tpls c="1">
-          <tpl fld="0" item="4"/>
-        </tpls>
-      </query>
-      <query mdx="[Measures].[Revenue Lost]">
-        <tpls c="1">
-          <tpl fld="0" item="5"/>
-        </tpls>
-      </query>
-    </queryCache>
-    <serverFormats count="3">
-      <serverFormat format="#,0.00"/>
-      <serverFormat format="#,0"/>
-      <serverFormat format="0.0%;-0.0%;0.0%"/>
-    </serverFormats>
-  </tupleCache>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFFEB3CE-48FE-43A9-B2EC-093110F1D33A}" name="ptRegions" cacheId="672" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CFFEB3CE-48FE-43A9-B2EC-093110F1D33A}" name="ptRegions" cacheId="105" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="H5:N14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
+  <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="8">
         <item x="0"/>
@@ -8122,7 +8305,6 @@
     <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -8249,7 +8431,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB99DD13-AEA4-44B1-AA72-3C157ECB39A5}" name="ptBundles" cacheId="693" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BB99DD13-AEA4-44B1-AA72-3C157ECB39A5}" name="ptBundles" cacheId="102" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A5:F19" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="7">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -8421,7 +8603,402 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B4DF028-BE2F-40C8-BB9B-04FB508D2FC8}" name="ptStatus" cacheId="690" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{432004A9-F0A8-4EDE-9E8B-041BA2C249DE}" name="ptProduct" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="I3:J8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="11"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{512F9654-2B46-4612-885C-B24FA56AD62F}" name="ptRegion" cacheId="84" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="E3:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="8">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="9">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="9"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F87F631C-5711-448B-BD3A-7E092271820D}" name="ptMonth" cacheId="87" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="12">
+        <item s="1" x="0"/>
+        <item s="1" x="1"/>
+        <item s="1" x="2"/>
+        <item s="1" x="3"/>
+        <item s="1" x="4"/>
+        <item s="1" x="5"/>
+        <item s="1" x="6"/>
+        <item s="1" x="7"/>
+        <item s="1" x="8"/>
+        <item s="1" x="9"/>
+        <item s="1" x="10"/>
+        <item s="1" x="11"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="38">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="4"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9B4DF028-BE2F-40C8-BB9B-04FB508D2FC8}" name="ptStatus" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="U3:Y9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -8581,10 +9158,10 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B1A2F2F-DA4A-4852-B925-D45BE29588AE}" name="ptFailure" cacheId="687" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B1A2F2F-DA4A-4852-B925-D45BE29588AE}" name="ptFailure" cacheId="96" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="Q3:R12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
+  <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="8">
         <item x="0"/>
@@ -8607,7 +9184,6 @@
       </autoSortScope>
     </pivotField>
     <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -8716,8 +9292,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C6241DC-5D61-49F6-913A-7490C00D011C}" name="ptChannel" cacheId="684" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8C6241DC-5D61-49F6-913A-7490C00D011C}" name="ptChannel" cacheId="93" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="M3:N8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -8809,402 +9385,6 @@
   <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
     <rowHierarchyUsage hierarchyUsage="13"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{432004A9-F0A8-4EDE-9E8B-041BA2C249DE}" name="ptProduct" cacheId="681" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="I3:J8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="11"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{512F9654-2B46-4612-885C-B24FA56AD62F}" name="ptRegion" cacheId="675" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="E3:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" sortType="descending" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="8">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="9">
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="9"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F87F631C-5711-448B-BD3A-7E092271820D}" name="ptMonth" cacheId="678" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="12">
-        <item s="1" x="0"/>
-        <item s="1" x="1"/>
-        <item s="1" x="2"/>
-        <item s="1" x="3"/>
-        <item s="1" x="4"/>
-        <item s="1" x="5"/>
-        <item s="1" x="6"/>
-        <item s="1" x="7"/>
-        <item s="1" x="8"/>
-        <item s="1" x="9"/>
-        <item s="1" x="10"/>
-        <item s="1" x="11"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Revenue " fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="38">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="4"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -9817,1645 +9997,1645 @@
       <c r="Z3" s="9"/>
     </row>
     <row r="4" spans="1:26" ht="9.9499999999999993" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="16" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="16" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="16" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
-      <c r="M5" s="16" t="s">
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="N5" s="17"/>
-      <c r="O5" s="17"/>
-      <c r="P5" s="16" t="s">
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="Q5" s="17"/>
-      <c r="R5" s="17"/>
-      <c r="S5" s="16" t="s">
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="T5" s="17"/>
-      <c r="U5" s="18"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="11" vm="1">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="25" vm="1">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Revenue]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>42723</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="19" vm="2">
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="21" vm="2">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Transaction Count]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>4233</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="23" vm="3">
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="32" vm="3">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Success Rate]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>0.80888258918025047</v>
       </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="19" vm="4">
+      <c r="K6" s="33"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="21" vm="4">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Active Customers]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>889</v>
       </c>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="11" vm="5">
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="25" vm="5">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Average Ticket]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>12.477511682242991</v>
       </c>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="11" vm="6">
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
+      <c r="S6" s="25" vm="6">
         <f>CUBEVALUE("ThisWorkbookDataModel","[Measures].[Revenue Lost]",Slicer_Region,Slicer_Segment,Slicer_Product,Slicer_Channel,Slicer_Quarter)</f>
         <v>5919.5</v>
       </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="14"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
+      <c r="T6" s="26"/>
+      <c r="U6" s="30"/>
+      <c r="V6" s="10"/>
+      <c r="W6" s="10"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+      <c r="Z6" s="10"/>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="12"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="12"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="15"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27"/>
-      <c r="Z7" s="27"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="27"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="27"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="10"/>
+      <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+      <c r="Z7" s="10"/>
     </row>
     <row r="8" spans="1:26" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
-      <c r="R8" s="27"/>
-      <c r="S8" s="27"/>
-      <c r="T8" s="27"/>
-      <c r="U8" s="27"/>
-      <c r="V8" s="27"/>
-      <c r="W8" s="27"/>
-      <c r="X8" s="27"/>
-      <c r="Y8" s="27"/>
-      <c r="Z8" s="27"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="10"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+      <c r="Z8" s="10"/>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A9" s="27"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="10"/>
+      <c r="J9" s="10"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="10"/>
+      <c r="W9" s="10"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+      <c r="Z9" s="10"/>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A10" s="27"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
-      <c r="R10" s="27"/>
-      <c r="S10" s="27"/>
-      <c r="T10" s="27"/>
-      <c r="U10" s="27"/>
-      <c r="V10" s="27"/>
-      <c r="W10" s="27"/>
-      <c r="X10" s="27"/>
-      <c r="Y10" s="27"/>
-      <c r="Z10" s="27"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="10"/>
+      <c r="W10" s="10"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+      <c r="Z10" s="10"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A11" s="27"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="10"/>
+      <c r="W11" s="10"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+      <c r="Z11" s="10"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A12" s="27"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
-      <c r="O12" s="27"/>
-      <c r="P12" s="27"/>
-      <c r="Q12" s="27"/>
-      <c r="R12" s="27"/>
-      <c r="S12" s="27"/>
-      <c r="T12" s="27"/>
-      <c r="U12" s="27"/>
-      <c r="V12" s="27"/>
-      <c r="W12" s="27"/>
-      <c r="X12" s="27"/>
-      <c r="Y12" s="27"/>
-      <c r="Z12" s="27"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="27"/>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A14" s="27"/>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="27"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A15" s="27"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="27"/>
-      <c r="X15" s="27"/>
-      <c r="Y15" s="27"/>
-      <c r="Z15" s="27"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="10"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="10"/>
+      <c r="W15" s="10"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+      <c r="Z15" s="10"/>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A16" s="27"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="27"/>
-      <c r="V16" s="27"/>
-      <c r="W16" s="27"/>
-      <c r="X16" s="27"/>
-      <c r="Y16" s="27"/>
-      <c r="Z16" s="27"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="10"/>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="10"/>
+      <c r="W16" s="10"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+      <c r="Z16" s="10"/>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="27"/>
-      <c r="V17" s="27"/>
-      <c r="W17" s="27"/>
-      <c r="X17" s="27"/>
-      <c r="Y17" s="27"/>
-      <c r="Z17" s="27"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="10"/>
+      <c r="W17" s="10"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
+      <c r="Z17" s="10"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A18" s="27"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="27"/>
-      <c r="V18" s="27"/>
-      <c r="W18" s="27"/>
-      <c r="X18" s="27"/>
-      <c r="Y18" s="27"/>
-      <c r="Z18" s="27"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+      <c r="P18" s="10"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="10"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="10"/>
+      <c r="W18" s="10"/>
+      <c r="X18" s="10"/>
+      <c r="Y18" s="10"/>
+      <c r="Z18" s="10"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A19" s="27"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="27"/>
-      <c r="L19" s="27"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="27"/>
-      <c r="V19" s="27"/>
-      <c r="W19" s="27"/>
-      <c r="X19" s="27"/>
-      <c r="Y19" s="27"/>
-      <c r="Z19" s="27"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10"/>
+      <c r="W19" s="10"/>
+      <c r="X19" s="10"/>
+      <c r="Y19" s="10"/>
+      <c r="Z19" s="10"/>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A20" s="27"/>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+      <c r="P20" s="10"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
+      <c r="S20" s="10"/>
+      <c r="T20" s="10"/>
+      <c r="U20" s="10"/>
+      <c r="V20" s="10"/>
+      <c r="W20" s="10"/>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10"/>
+      <c r="Z20" s="10"/>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="27"/>
-      <c r="Y21" s="27"/>
-      <c r="Z21" s="27"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A22" s="27"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="27"/>
-      <c r="X22" s="27"/>
-      <c r="Y22" s="27"/>
-      <c r="Z22" s="27"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A23" s="27"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A24" s="27"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="27"/>
-      <c r="X24" s="27"/>
-      <c r="Y24" s="27"/>
-      <c r="Z24" s="27"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="10"/>
+      <c r="T24" s="10"/>
+      <c r="U24" s="10"/>
+      <c r="V24" s="10"/>
+      <c r="W24" s="10"/>
+      <c r="X24" s="10"/>
+      <c r="Y24" s="10"/>
+      <c r="Z24" s="10"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="27"/>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
+      <c r="S25" s="10"/>
+      <c r="T25" s="10"/>
+      <c r="U25" s="10"/>
+      <c r="V25" s="10"/>
+      <c r="W25" s="10"/>
+      <c r="X25" s="10"/>
+      <c r="Y25" s="10"/>
+      <c r="Z25" s="10"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A26" s="27"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="10"/>
+      <c r="V26" s="10"/>
+      <c r="W26" s="10"/>
+      <c r="X26" s="10"/>
+      <c r="Y26" s="10"/>
+      <c r="Z26" s="10"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="27"/>
-      <c r="W27" s="27"/>
-      <c r="X27" s="27"/>
-      <c r="Y27" s="27"/>
-      <c r="Z27" s="27"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
+      <c r="S27" s="10"/>
+      <c r="T27" s="10"/>
+      <c r="U27" s="10"/>
+      <c r="V27" s="10"/>
+      <c r="W27" s="10"/>
+      <c r="X27" s="10"/>
+      <c r="Y27" s="10"/>
+      <c r="Z27" s="10"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="27"/>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="10"/>
+      <c r="U28" s="10"/>
+      <c r="V28" s="10"/>
+      <c r="W28" s="10"/>
+      <c r="X28" s="10"/>
+      <c r="Y28" s="10"/>
+      <c r="Z28" s="10"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
+      <c r="S29" s="10"/>
+      <c r="T29" s="10"/>
+      <c r="U29" s="10"/>
+      <c r="V29" s="10"/>
+      <c r="W29" s="10"/>
+      <c r="X29" s="10"/>
+      <c r="Y29" s="10"/>
+      <c r="Z29" s="10"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="27"/>
-      <c r="V30" s="27"/>
-      <c r="W30" s="27"/>
-      <c r="X30" s="27"/>
-      <c r="Y30" s="27"/>
-      <c r="Z30" s="27"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
+      <c r="S30" s="10"/>
+      <c r="T30" s="10"/>
+      <c r="U30" s="10"/>
+      <c r="V30" s="10"/>
+      <c r="W30" s="10"/>
+      <c r="X30" s="10"/>
+      <c r="Y30" s="10"/>
+      <c r="Z30" s="10"/>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-      <c r="W31" s="27"/>
-      <c r="X31" s="27"/>
-      <c r="Y31" s="27"/>
-      <c r="Z31" s="27"/>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10"/>
+      <c r="W31" s="10"/>
+      <c r="X31" s="10"/>
+      <c r="Y31" s="10"/>
+      <c r="Z31" s="10"/>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A32" s="27"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+      <c r="I32" s="10"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
+      <c r="S32" s="10"/>
+      <c r="T32" s="10"/>
+      <c r="U32" s="10"/>
+      <c r="V32" s="10"/>
+      <c r="W32" s="10"/>
+      <c r="X32" s="10"/>
+      <c r="Y32" s="10"/>
+      <c r="Z32" s="10"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
-      <c r="W33" s="27"/>
-      <c r="X33" s="27"/>
-      <c r="Y33" s="27"/>
-      <c r="Z33" s="27"/>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
+      <c r="S33" s="10"/>
+      <c r="T33" s="10"/>
+      <c r="U33" s="10"/>
+      <c r="V33" s="10"/>
+      <c r="W33" s="10"/>
+      <c r="X33" s="10"/>
+      <c r="Y33" s="10"/>
+      <c r="Z33" s="10"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34" s="27"/>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="27"/>
-      <c r="W34" s="27"/>
-      <c r="X34" s="27"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="27"/>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="10"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="10"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
+      <c r="S34" s="10"/>
+      <c r="T34" s="10"/>
+      <c r="U34" s="10"/>
+      <c r="V34" s="10"/>
+      <c r="W34" s="10"/>
+      <c r="X34" s="10"/>
+      <c r="Y34" s="10"/>
+      <c r="Z34" s="10"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="27"/>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="27"/>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="10"/>
+      <c r="V35" s="10"/>
+      <c r="W35" s="10"/>
+      <c r="X35" s="10"/>
+      <c r="Y35" s="10"/>
+      <c r="Z35" s="10"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="27"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="27"/>
-      <c r="V36" s="27"/>
-      <c r="W36" s="27"/>
-      <c r="X36" s="27"/>
-      <c r="Y36" s="27"/>
-      <c r="Z36" s="27"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="10"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
+      <c r="S36" s="10"/>
+      <c r="T36" s="10"/>
+      <c r="U36" s="10"/>
+      <c r="V36" s="10"/>
+      <c r="W36" s="10"/>
+      <c r="X36" s="10"/>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="10"/>
+      <c r="K37" s="10"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="10"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
+      <c r="S37" s="10"/>
+      <c r="T37" s="10"/>
+      <c r="U37" s="10"/>
+      <c r="V37" s="10"/>
+      <c r="W37" s="10"/>
+      <c r="X37" s="10"/>
+      <c r="Y37" s="10"/>
+      <c r="Z37" s="10"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="27"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="27"/>
-      <c r="V38" s="27"/>
-      <c r="W38" s="27"/>
-      <c r="X38" s="27"/>
-      <c r="Y38" s="27"/>
-      <c r="Z38" s="27"/>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="10"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
+      <c r="S38" s="10"/>
+      <c r="T38" s="10"/>
+      <c r="U38" s="10"/>
+      <c r="V38" s="10"/>
+      <c r="W38" s="10"/>
+      <c r="X38" s="10"/>
+      <c r="Y38" s="10"/>
+      <c r="Z38" s="10"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="27"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="27"/>
-      <c r="W39" s="27"/>
-      <c r="X39" s="27"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="27"/>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="10"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
+      <c r="S39" s="10"/>
+      <c r="T39" s="10"/>
+      <c r="U39" s="10"/>
+      <c r="V39" s="10"/>
+      <c r="W39" s="10"/>
+      <c r="X39" s="10"/>
+      <c r="Y39" s="10"/>
+      <c r="Z39" s="10"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+      <c r="K40" s="10"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
+      <c r="S40" s="10"/>
+      <c r="T40" s="10"/>
+      <c r="U40" s="10"/>
+      <c r="V40" s="10"/>
+      <c r="W40" s="10"/>
+      <c r="X40" s="10"/>
+      <c r="Y40" s="10"/>
+      <c r="Z40" s="10"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="27"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="27"/>
-      <c r="W41" s="27"/>
-      <c r="X41" s="27"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="27"/>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="10"/>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
+      <c r="S41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10"/>
+      <c r="V41" s="10"/>
+      <c r="W41" s="10"/>
+      <c r="X41" s="10"/>
+      <c r="Y41" s="10"/>
+      <c r="Z41" s="10"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="27"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="27"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-      <c r="W42" s="27"/>
-      <c r="X42" s="27"/>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="27"/>
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="10"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="10"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
+      <c r="S42" s="10"/>
+      <c r="T42" s="10"/>
+      <c r="U42" s="10"/>
+      <c r="V42" s="10"/>
+      <c r="W42" s="10"/>
+      <c r="X42" s="10"/>
+      <c r="Y42" s="10"/>
+      <c r="Z42" s="10"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="27"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="10"/>
+      <c r="H43" s="10"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
+      <c r="S43" s="10"/>
+      <c r="T43" s="10"/>
+      <c r="U43" s="10"/>
+      <c r="V43" s="10"/>
+      <c r="W43" s="10"/>
+      <c r="X43" s="10"/>
+      <c r="Y43" s="10"/>
+      <c r="Z43" s="10"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="27"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="27"/>
-      <c r="R44" s="27"/>
-      <c r="S44" s="27"/>
-      <c r="T44" s="27"/>
-      <c r="U44" s="27"/>
-      <c r="V44" s="27"/>
-      <c r="W44" s="27"/>
-      <c r="X44" s="27"/>
-      <c r="Y44" s="27"/>
-      <c r="Z44" s="27"/>
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="10"/>
+      <c r="T44" s="10"/>
+      <c r="U44" s="10"/>
+      <c r="V44" s="10"/>
+      <c r="W44" s="10"/>
+      <c r="X44" s="10"/>
+      <c r="Y44" s="10"/>
+      <c r="Z44" s="10"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="27"/>
-      <c r="G45" s="27"/>
-      <c r="H45" s="27"/>
-      <c r="I45" s="27"/>
-      <c r="J45" s="27"/>
-      <c r="K45" s="27"/>
-      <c r="L45" s="27"/>
-      <c r="M45" s="27"/>
-      <c r="N45" s="27"/>
-      <c r="O45" s="27"/>
-      <c r="P45" s="27"/>
-      <c r="Q45" s="27"/>
-      <c r="R45" s="27"/>
-      <c r="S45" s="27"/>
-      <c r="T45" s="27"/>
-      <c r="U45" s="27"/>
-      <c r="V45" s="27"/>
-      <c r="W45" s="27"/>
-      <c r="X45" s="27"/>
-      <c r="Y45" s="27"/>
-      <c r="Z45" s="27"/>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+      <c r="K45" s="10"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="10"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
+      <c r="S45" s="10"/>
+      <c r="T45" s="10"/>
+      <c r="U45" s="10"/>
+      <c r="V45" s="10"/>
+      <c r="W45" s="10"/>
+      <c r="X45" s="10"/>
+      <c r="Y45" s="10"/>
+      <c r="Z45" s="10"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="27"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="10"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="10"/>
+      <c r="H46" s="10"/>
+      <c r="I46" s="10"/>
+      <c r="J46" s="10"/>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="10"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
+      <c r="S46" s="10"/>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10"/>
+      <c r="V46" s="10"/>
+      <c r="W46" s="10"/>
+      <c r="X46" s="10"/>
+      <c r="Y46" s="10"/>
+      <c r="Z46" s="10"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="27"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="27"/>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="27"/>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-      <c r="W47" s="27"/>
-      <c r="X47" s="27"/>
-      <c r="Y47" s="27"/>
-      <c r="Z47" s="27"/>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="10"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="J47" s="10"/>
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="10"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
+      <c r="S47" s="10"/>
+      <c r="T47" s="10"/>
+      <c r="U47" s="10"/>
+      <c r="V47" s="10"/>
+      <c r="W47" s="10"/>
+      <c r="X47" s="10"/>
+      <c r="Y47" s="10"/>
+      <c r="Z47" s="10"/>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="27"/>
-      <c r="B48" s="27"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="27"/>
-      <c r="G48" s="27"/>
-      <c r="H48" s="27"/>
-      <c r="I48" s="27"/>
-      <c r="J48" s="27"/>
-      <c r="K48" s="27"/>
-      <c r="L48" s="27"/>
-      <c r="M48" s="27"/>
-      <c r="N48" s="27"/>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-      <c r="Q48" s="27"/>
-      <c r="R48" s="27"/>
-      <c r="S48" s="27"/>
-      <c r="T48" s="27"/>
-      <c r="U48" s="27"/>
-      <c r="V48" s="27"/>
-      <c r="W48" s="27"/>
-      <c r="X48" s="27"/>
-      <c r="Y48" s="27"/>
-      <c r="Z48" s="27"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
+      <c r="X48" s="10"/>
+      <c r="Y48" s="10"/>
+      <c r="Z48" s="10"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="10"/>
+      <c r="D49" s="10"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
+      <c r="Y49" s="10"/>
+      <c r="Z49" s="10"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="27"/>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="27"/>
-      <c r="S50" s="27"/>
-      <c r="T50" s="27"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="27"/>
-      <c r="W50" s="27"/>
-      <c r="X50" s="27"/>
-      <c r="Y50" s="27"/>
-      <c r="Z50" s="27"/>
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
+      <c r="X50" s="10"/>
+      <c r="Y50" s="10"/>
+      <c r="Z50" s="10"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="27"/>
-      <c r="E51" s="27"/>
-      <c r="F51" s="27"/>
-      <c r="G51" s="27"/>
-      <c r="H51" s="27"/>
-      <c r="I51" s="27"/>
-      <c r="J51" s="27"/>
-      <c r="K51" s="27"/>
-      <c r="L51" s="27"/>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
-      <c r="T51" s="27"/>
-      <c r="U51" s="27"/>
-      <c r="V51" s="27"/>
-      <c r="W51" s="27"/>
-      <c r="X51" s="27"/>
-      <c r="Y51" s="27"/>
-      <c r="Z51" s="27"/>
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
+      <c r="X51" s="10"/>
+      <c r="Y51" s="10"/>
+      <c r="Z51" s="10"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="10"/>
+      <c r="D52" s="10"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
+      <c r="X52" s="10"/>
+      <c r="Y52" s="10"/>
+      <c r="Z52" s="10"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="27"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="27"/>
-      <c r="H53" s="27"/>
-      <c r="I53" s="27"/>
-      <c r="J53" s="27"/>
-      <c r="K53" s="27"/>
-      <c r="L53" s="27"/>
-      <c r="M53" s="27"/>
-      <c r="N53" s="27"/>
-      <c r="O53" s="27"/>
-      <c r="P53" s="27"/>
-      <c r="Q53" s="27"/>
-      <c r="R53" s="27"/>
-      <c r="S53" s="27"/>
-      <c r="T53" s="27"/>
-      <c r="U53" s="27"/>
-      <c r="V53" s="27"/>
-      <c r="W53" s="27"/>
-      <c r="X53" s="27"/>
-      <c r="Y53" s="27"/>
-      <c r="Z53" s="27"/>
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A54" s="27"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="27"/>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="27"/>
-      <c r="R54" s="27"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="W54" s="27"/>
-      <c r="X54" s="27"/>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="27"/>
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="27"/>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="10"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
+      <c r="S55" s="10"/>
+      <c r="T55" s="10"/>
+      <c r="U55" s="10"/>
+      <c r="V55" s="10"/>
+      <c r="W55" s="10"/>
+      <c r="X55" s="10"/>
+      <c r="Y55" s="10"/>
+      <c r="Z55" s="10"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="27"/>
-      <c r="B56" s="27"/>
-      <c r="C56" s="27"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="27"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="27"/>
-      <c r="H56" s="27"/>
-      <c r="I56" s="27"/>
-      <c r="J56" s="27"/>
-      <c r="K56" s="27"/>
-      <c r="L56" s="27"/>
-      <c r="M56" s="27"/>
-      <c r="N56" s="27"/>
-      <c r="O56" s="27"/>
-      <c r="P56" s="27"/>
-      <c r="Q56" s="27"/>
-      <c r="R56" s="27"/>
-      <c r="S56" s="27"/>
-      <c r="T56" s="27"/>
-      <c r="U56" s="27"/>
-      <c r="V56" s="27"/>
-      <c r="W56" s="27"/>
-      <c r="X56" s="27"/>
-      <c r="Y56" s="27"/>
-      <c r="Z56" s="27"/>
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="10"/>
+      <c r="K56" s="10"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
+      <c r="S56" s="10"/>
+      <c r="T56" s="10"/>
+      <c r="U56" s="10"/>
+      <c r="V56" s="10"/>
+      <c r="W56" s="10"/>
+      <c r="X56" s="10"/>
+      <c r="Y56" s="10"/>
+      <c r="Z56" s="10"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A57" s="27"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="27"/>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="27"/>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="27"/>
-      <c r="Y57" s="27"/>
-      <c r="Z57" s="27"/>
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="10"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
+      <c r="S57" s="10"/>
+      <c r="T57" s="10"/>
+      <c r="U57" s="10"/>
+      <c r="V57" s="10"/>
+      <c r="W57" s="10"/>
+      <c r="X57" s="10"/>
+      <c r="Y57" s="10"/>
+      <c r="Z57" s="10"/>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A58" s="27"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="10"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+      <c r="K58" s="10"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="10"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
+      <c r="S58" s="10"/>
+      <c r="T58" s="10"/>
+      <c r="U58" s="10"/>
+      <c r="V58" s="10"/>
+      <c r="W58" s="10"/>
+      <c r="X58" s="10"/>
+      <c r="Y58" s="10"/>
+      <c r="Z58" s="10"/>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="27"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
-      <c r="Q59" s="27"/>
-      <c r="R59" s="27"/>
-      <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-      <c r="U59" s="27"/>
-      <c r="V59" s="27"/>
-      <c r="W59" s="27"/>
-      <c r="X59" s="27"/>
-      <c r="Y59" s="27"/>
-      <c r="Z59" s="27"/>
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="10"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
+      <c r="K59" s="10"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="10"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
+      <c r="S59" s="10"/>
+      <c r="T59" s="10"/>
+      <c r="U59" s="10"/>
+      <c r="V59" s="10"/>
+      <c r="W59" s="10"/>
+      <c r="X59" s="10"/>
+      <c r="Y59" s="10"/>
+      <c r="Z59" s="10"/>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A60" s="27"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="27"/>
-      <c r="W60" s="27"/>
-      <c r="X60" s="27"/>
-      <c r="Y60" s="27"/>
-      <c r="Z60" s="27"/>
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="10"/>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="10"/>
+      <c r="K60" s="10"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="10"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
+      <c r="S60" s="10"/>
+      <c r="T60" s="10"/>
+      <c r="U60" s="10"/>
+      <c r="V60" s="10"/>
+      <c r="W60" s="10"/>
+      <c r="X60" s="10"/>
+      <c r="Y60" s="10"/>
+      <c r="Z60" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D6:F7"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="G6:I7"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="J6:L7"/>
     <mergeCell ref="M5:O5"/>
     <mergeCell ref="M6:O7"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="P6:R7"/>
     <mergeCell ref="S5:U5"/>
     <mergeCell ref="S6:U7"/>
-    <mergeCell ref="D5:F5"/>
-    <mergeCell ref="D6:F7"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G6:I7"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="J6:L7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -12428,388 +12608,388 @@
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" style="29" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" style="29" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="29" customWidth="1"/>
-    <col min="4" max="4" width="60.7109375" style="29" customWidth="1"/>
-    <col min="5" max="5" width="52.7109375" style="29" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" width="16.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" style="12" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="12" customWidth="1"/>
+    <col min="4" max="4" width="60.7109375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="52.7109375" style="12" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="42" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="11" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="120" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="13" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="14" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="32" t="s">
+      <c r="A5" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="12">
         <v>4055</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="12" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="12">
         <v>3338</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="12">
         <v>3196</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="12" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="12">
         <v>2975</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="12" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="12">
         <v>501</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="12" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="12">
         <v>435</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="12" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="12">
         <v>312</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="12" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="12">
         <v>139</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="12" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="12">
         <v>110</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="12" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="12">
         <v>68</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="12" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="12">
         <v>55</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="12">
         <v>7</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="12" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="14" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C21" s="32" t="s">
+      <c r="C21" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D21" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="15" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="12">
         <v>800</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="12">
         <v>1200</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="12">
         <v>1500</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="12">
         <v>800</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D26" s="29">
+      <c r="D26" s="12">
         <v>800</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E26" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D27" s="29">
+      <c r="D27" s="12">
         <v>1500</v>
       </c>
-      <c r="E27" s="29">
+      <c r="E27" s="12">
         <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="12">
         <v>2000</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="12">
         <v>20</v>
       </c>
     </row>
@@ -12823,186 +13003,186 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="29" customWidth="1"/>
-    <col min="2" max="2" width="120.7109375" style="29" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="29"/>
+    <col min="1" max="1" width="24.7109375" style="12" customWidth="1"/>
+    <col min="2" max="2" width="120.7109375" style="12" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="17" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="16" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="16" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="16" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="16" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="16" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="17" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="16" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="16" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="16" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="16" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="16" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="16" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="16" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="16" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="16" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+      <c r="A17" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="16" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="16" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="16" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+      <c r="A21" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="16" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="B22" s="33" t="s">
+      <c r="B22" s="16" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
+      <c r="A23" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="B23" s="33" t="s">
+      <c r="B23" s="16" t="s">
         <v>169</v>
       </c>
     </row>
